--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -23643,7 +23643,7 @@
         <v>2020</v>
       </c>
       <c r="H277" t="s">
-        <v>2031</v>
+        <v>2039</v>
       </c>
       <c r="I277" t="s">
         <v>2140</v>

--- a/SaidaSemITGATEAutoCompleto.xlsx
+++ b/SaidaSemITGATEAutoCompleto.xlsx
@@ -37984,7 +37984,7 @@
         <v>2032</v>
       </c>
       <c r="H702" t="s">
-        <v>2041</v>
+        <v>2059</v>
       </c>
       <c r="I702" t="s">
         <v>2138</v>
